--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-21.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +613,88 @@
         <v>35.71</v>
       </c>
       <c r="T2" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Danish Cup</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Vanlose x Nykobing FC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vanlose</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nykobing FC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>200</v>
+      </c>
+      <c r="S3" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T3" t="n">
         <v>34.1</v>
       </c>
     </row>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-21.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-21.xlsx
@@ -664,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.54</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
